--- a/business_forms/043_real_estate_seller_intake_form--business_forms.xlsx
+++ b/business_forms/043_real_estate_seller_intake_form--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -849,8 +849,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -878,12 +878,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'single_family'}</t>
+          <t>single_family</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'single_family'}</t>
+          <t>single family</t>
         </is>
       </c>
     </row>
@@ -895,12 +895,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'multi_family'}</t>
+          <t>multi_family</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'multi_family'}</t>
+          <t>multi family</t>
         </is>
       </c>
     </row>
@@ -912,12 +912,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'commercial'}</t>
+          <t>commercial</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'commercial'}</t>
+          <t>commercial</t>
         </is>
       </c>
     </row>
@@ -929,12 +929,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'active'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'active'}</t>
+          <t>active</t>
         </is>
       </c>
     </row>
@@ -946,12 +946,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
     </row>
@@ -963,12 +963,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'sold'}</t>
+          <t>sold</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'sold'}</t>
+          <t>sold</t>
         </is>
       </c>
     </row>
@@ -980,12 +980,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'new_york'}</t>
+          <t>new_york</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'new_york'}</t>
+          <t>new york</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'san_francisco'}</t>
+          <t>san_francisco</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'san_francisco'}</t>
+          <t>san francisco</t>
         </is>
       </c>
     </row>
@@ -1014,12 +1014,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'los_angeles'}</t>
+          <t>los_angeles</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'los_angeles'}</t>
+          <t>los angeles</t>
         </is>
       </c>
     </row>
@@ -1031,12 +1031,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'ca'}</t>
+          <t>ca</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'ca'}</t>
+          <t>ca</t>
         </is>
       </c>
     </row>
@@ -1048,12 +1048,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'ny'}</t>
+          <t>ny</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'ny'}</t>
+          <t>ny</t>
         </is>
       </c>
     </row>
@@ -1065,12 +1065,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'tx'}</t>
+          <t>tx</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'tx'}</t>
+          <t>tx</t>
         </is>
       </c>
     </row>
